--- a/ig/DM-37/CodeSystem-TRE-R21-Fonction.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R21-Fonction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -464,6 +464,21 @@
   </si>
   <si>
     <t>Docteur junior</t>
+  </si>
+  <si>
+    <t>Par décret n°2018- 571 en date du 03 juillet 2018, les étudiants internes de 3e cycle en médecine, pharmacie ou biologie médicale qui accomplissent la phase 3 dite « de consolidation » sont dorénavant dénommés « Docteurs juniors ».  Lorsqu'il a validé l'ensemble des connaissances et compétences nécessaires à la validation de la phase 2 de la spécialité suivie, soutenu avec succès la thèse mentionnée à l'article R. 632-23 du code de l'éducation et obtenu le diplôme d'Etat de docteur en médecine, en pharmacie, ou en odontologie, l'étudiant de troisième cycle est nommé en qualité de docteur junior par le directeur général du centre hospitalier universitaire de rattachement. Les premières nominations de docteurs juniors sont intervenues à compter du 1er novembre 2020.</t>
+  </si>
+  <si>
+    <t>FON-58</t>
+  </si>
+  <si>
+    <t>Activité en piscine ou bassin</t>
+  </si>
+  <si>
+    <t>FON-59</t>
+  </si>
+  <si>
+    <t>Gérant d'antenne</t>
   </si>
   <si>
     <t>FON-AU</t>
@@ -843,7 +858,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1086,7 +1101,9 @@
       <c r="C20" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>87</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -1458,19 +1475,45 @@
       <c r="C51" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>150</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="D54" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
